--- a/main/ig/StructureDefinition-dmi-invoice.xlsx
+++ b/main/ig/StructureDefinition-dmi-invoice.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.0</t>
+    <t>3.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T10:37:28+00:00</t>
+    <t>2026-03-05T09:47:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-invoice.xlsx
+++ b/main/ig/StructureDefinition-dmi-invoice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T09:47:44+00:00</t>
+    <t>2026-03-05T10:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-invoice.xlsx
+++ b/main/ig/StructureDefinition-dmi-invoice.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2295" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2309" uniqueCount="393">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:00:25+00:00</t>
+    <t>2026-03-05T10:01:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -266,7 +266,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
   </si>
   <si>
     <t>FT1</t>
@@ -316,10 +316,17 @@
     <t>Resource.meta</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>Invoice.implicitRules</t>
   </si>
   <si>
@@ -339,6 +346,9 @@
     <t>Resource.implicitRules</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>Invoice.language</t>
   </si>
   <si>
@@ -416,26 +426,33 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Invoice.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
   </si>
   <si>
     <t xml:space="preserve">Extension
 </t>
   </si>
   <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
 </t>
   </si>
   <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
     <t>open</t>
   </si>
   <si>
@@ -462,15 +479,7 @@
     <t>Extension créée dans ce volet pour représenter une facture.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>Invoice.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
   </si>
   <si>
     <t>Extensions that cannot be ignored</t>
@@ -480,9 +489,6 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -546,22 +552,13 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Invoice.identifier:refFacture.extension</t>
   </si>
   <si>
     <t>Invoice.identifier.extension</t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -718,7 +715,15 @@
     <t>Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
+    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
+Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
+  </si>
+  <si>
     <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
   </si>
   <si>
     <t>CX.7 + CX.8</t>
@@ -747,6 +752,10 @@
   </si>
   <si>
     <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
@@ -802,6 +811,9 @@
     <t>The current state of the Invoice.</t>
   </si>
   <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
     <t>Codes identifying the lifecycle stage of an Invoice.</t>
   </si>
   <si>
@@ -842,6 +854,9 @@
     <t>Type of Invoice depending on domain, realm an usage (e.g. internal/external, dental, preliminary).</t>
   </si>
   <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+  </si>
+  <si>
     <t>FT1.7</t>
   </si>
   <si>
@@ -871,6 +886,9 @@
     <t>The individual or set of individuals receiving the goods and services billed in this invoice.</t>
   </si>
   <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
     <t>Links the event to the Patient context.</t>
   </si>
   <si>
@@ -1034,6 +1052,9 @@
     <t>Systems posting the ChargeItems might not always be able to determine, which accounts the Items need to be places into. It is up to the potprocessing Financial System to apply internal rules to decide based on the Encounter/EpisodeOfCare/Patient/Coverage context and the type of ChargeItem, which Account is appropriate.</t>
   </si>
   <si>
+    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
+  </si>
+  <si>
     <t>Invoice.lineItem</t>
   </si>
   <si>
@@ -1065,6 +1086,9 @@
     <t>Sequence in which the items appear on the invoice.</t>
   </si>
   <si>
+    <t>32 bit number; for values larger than this, use decimal</t>
+  </si>
+  <si>
     <t>Invoice.lineItem.chargeItem[x]</t>
   </si>
   <si>
@@ -1152,6 +1176,9 @@
     <t>The amount calculated for this component.</t>
   </si>
   <si>
+    <t>MO</t>
+  </si>
+  <si>
     <t>Invoice.totalPriceComponent</t>
   </si>
   <si>
@@ -1206,6 +1233,9 @@
   </si>
   <si>
     <t>Comments made about the invoice by the issuer, subject, or other participants.</t>
+  </si>
+  <si>
+    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
   </si>
   <si>
     <t>NTE</t>
@@ -2002,16 +2032,16 @@
         <v>87</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AM4" t="s" s="2">
         <v>77</v>
@@ -2022,10 +2052,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2048,16 +2078,16 @@
         <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2107,7 +2137,7 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -2116,16 +2146,16 @@
         <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AM5" t="s" s="2">
         <v>77</v>
@@ -2136,10 +2166,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2162,16 +2192,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2197,13 +2227,13 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>77</v>
@@ -2221,7 +2251,7 @@
         <v>77</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
@@ -2230,16 +2260,16 @@
         <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AM6" t="s" s="2">
         <v>77</v>
@@ -2250,14 +2280,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2276,16 +2306,16 @@
         <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2335,7 +2365,7 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -2344,16 +2374,16 @@
         <v>87</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>77</v>
@@ -2364,14 +2394,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2390,16 +2420,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2449,7 +2479,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2467,7 +2497,7 @@
         <v>77</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>77</v>
@@ -2478,14 +2508,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2504,15 +2534,17 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="N9" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>77</v>
@@ -2549,17 +2581,19 @@
         <v>77</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AC9" s="2"/>
+        <v>139</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="AD9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2568,16 +2602,16 @@
         <v>79</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>77</v>
@@ -2588,13 +2622,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>77</v>
@@ -2616,13 +2650,13 @@
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2673,7 +2707,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2682,10 +2716,10 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>144</v>
+        <v>99</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
@@ -2702,14 +2736,14 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2728,19 +2762,19 @@
         <v>77</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>77</v>
@@ -2777,19 +2811,19 @@
         <v>77</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="AD11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>77</v>
+        <v>141</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2798,16 +2832,16 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>77</v>
@@ -2818,10 +2852,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2829,7 +2863,7 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>79</v>
@@ -2844,17 +2878,17 @@
         <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -2891,17 +2925,17 @@
         <v>77</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AC12" s="2"/>
       <c r="AD12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2910,19 +2944,19 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>77</v>
@@ -2930,13 +2964,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>77</v>
@@ -2958,17 +2992,17 @@
         <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>77</v>
@@ -3017,7 +3051,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3026,19 +3060,19 @@
         <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>77</v>
@@ -3046,10 +3080,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3072,13 +3106,13 @@
         <v>77</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3129,7 +3163,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3147,7 +3181,7 @@
         <v>77</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>170</v>
+        <v>108</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>77</v>
@@ -3158,14 +3192,14 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3184,16 +3218,16 @@
         <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>173</v>
+        <v>136</v>
       </c>
       <c r="M15" t="s" s="2">
         <v>174</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3231,19 +3265,19 @@
         <v>77</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="AC15" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3252,16 +3286,16 @@
         <v>79</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>170</v>
+        <v>101</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>77</v>
@@ -3272,10 +3306,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3298,19 +3332,19 @@
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3335,49 +3369,49 @@
         <v>77</v>
       </c>
       <c r="X16" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Y16" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="Z16" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="Z16" t="s" s="2">
+      <c r="AA16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="AA16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF16" t="s" s="2">
+      <c r="AG16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK16" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AL16" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK16" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
@@ -3388,10 +3422,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3414,19 +3448,19 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>77</v>
@@ -3436,64 +3470,64 @@
         <v>77</v>
       </c>
       <c r="S17" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X17" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="T17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X17" t="s" s="2">
+      <c r="Y17" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="Y17" t="s" s="2">
+      <c r="Z17" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="Z17" t="s" s="2">
+      <c r="AA17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AA17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF17" t="s" s="2">
+      <c r="AG17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK17" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="AG17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK17" t="s" s="2">
-        <v>200</v>
-      </c>
       <c r="AL17" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
@@ -3504,10 +3538,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>202</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3530,19 +3564,19 @@
         <v>88</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -3555,61 +3589,61 @@
         <v>77</v>
       </c>
       <c r="T18" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="U18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF18" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="U18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF18" t="s" s="2">
+      <c r="AG18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK18" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="AG18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK18" t="s" s="2">
+      <c r="AL18" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -3620,10 +3654,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3646,16 +3680,16 @@
         <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3669,61 +3703,61 @@
         <v>77</v>
       </c>
       <c r="T19" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF19" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="U19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF19" t="s" s="2">
+      <c r="AG19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK19" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="AG19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH19" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ19" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK19" t="s" s="2">
+      <c r="AL19" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -3734,10 +3768,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3760,15 +3794,17 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>77</v>
@@ -3826,16 +3862,16 @@
         <v>87</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>99</v>
+        <v>226</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
@@ -3846,10 +3882,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3872,16 +3908,16 @@
         <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3931,7 +3967,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3940,16 +3976,16 @@
         <v>87</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>99</v>
+        <v>236</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
@@ -3960,13 +3996,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>77</v>
@@ -3988,17 +4024,17 @@
         <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -4047,7 +4083,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4056,19 +4092,19 @@
         <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>77</v>
@@ -4076,10 +4112,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4102,13 +4138,13 @@
         <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4159,7 +4195,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4177,7 +4213,7 @@
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>170</v>
+        <v>108</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -4188,14 +4224,14 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4214,16 +4250,16 @@
         <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>173</v>
+        <v>136</v>
       </c>
       <c r="M24" t="s" s="2">
         <v>174</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4261,19 +4297,19 @@
         <v>77</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="AC24" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AF24" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4282,16 +4318,16 @@
         <v>79</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>170</v>
+        <v>101</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -4302,10 +4338,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4328,19 +4364,19 @@
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4365,49 +4401,49 @@
         <v>77</v>
       </c>
       <c r="X25" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Y25" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="Y25" t="s" s="2">
+      <c r="Z25" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="Z25" t="s" s="2">
+      <c r="AA25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="AA25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF25" t="s" s="2">
+      <c r="AG25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AL25" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="AG25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ25" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK25" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4418,10 +4454,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4444,19 +4480,19 @@
         <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4466,7 +4502,7 @@
         <v>77</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>77</v>
@@ -4481,49 +4517,49 @@
         <v>77</v>
       </c>
       <c r="X26" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="Y26" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="Y26" t="s" s="2">
+      <c r="Z26" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="Z26" t="s" s="2">
+      <c r="AA26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AA26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF26" t="s" s="2">
+      <c r="AG26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK26" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="AG26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ26" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK26" t="s" s="2">
-        <v>200</v>
-      </c>
       <c r="AL26" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4534,10 +4570,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4560,19 +4596,19 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4585,61 +4621,61 @@
         <v>77</v>
       </c>
       <c r="T27" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="U27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF27" t="s" s="2">
+      <c r="AG27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK27" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="AG27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ27" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK27" t="s" s="2">
+      <c r="AL27" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -4650,10 +4686,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4676,16 +4712,16 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4699,61 +4735,61 @@
         <v>77</v>
       </c>
       <c r="T28" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="U28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF28" t="s" s="2">
+      <c r="AG28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK28" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="AG28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK28" t="s" s="2">
+      <c r="AL28" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -4764,10 +4800,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4790,15 +4826,17 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -4856,16 +4894,16 @@
         <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>99</v>
+        <v>226</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
@@ -4876,10 +4914,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4902,16 +4940,16 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4961,7 +4999,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4970,16 +5008,16 @@
         <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>99</v>
+        <v>236</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
@@ -4990,10 +5028,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5016,15 +5054,17 @@
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -5049,13 +5089,13 @@
         <v>77</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>77</v>
@@ -5073,7 +5113,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>87</v>
@@ -5082,19 +5122,19 @@
         <v>87</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -5102,10 +5142,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5128,16 +5168,16 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5187,7 +5227,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5196,16 +5236,16 @@
         <v>87</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -5216,14 +5256,14 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5242,15 +5282,17 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5299,7 +5341,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5308,34 +5350,34 @@
         <v>87</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5354,17 +5396,19 @@
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="O34" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5413,7 +5457,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5422,30 +5466,30 @@
         <v>87</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>99</v>
+        <v>236</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5468,15 +5512,17 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5525,7 +5571,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5534,30 +5580,30 @@
         <v>87</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>99</v>
+        <v>236</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5580,16 +5626,16 @@
         <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5639,7 +5685,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5648,19 +5694,19 @@
         <v>87</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>77</v>
@@ -5668,10 +5714,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5694,13 +5740,13 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5751,7 +5797,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5760,16 +5806,16 @@
         <v>79</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -5780,10 +5826,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5806,13 +5852,13 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5863,7 +5909,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5881,7 +5927,7 @@
         <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>170</v>
+        <v>108</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
@@ -5892,14 +5938,14 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -5918,16 +5964,16 @@
         <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>173</v>
+        <v>136</v>
       </c>
       <c r="M39" t="s" s="2">
         <v>174</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5965,19 +6011,19 @@
         <v>77</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>77</v>
+        <v>141</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5986,16 +6032,16 @@
         <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>170</v>
+        <v>101</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
@@ -6006,14 +6052,14 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6032,19 +6078,19 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>77</v>
@@ -6093,7 +6139,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6102,16 +6148,16 @@
         <v>79</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -6122,10 +6168,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6148,15 +6194,17 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>77</v>
@@ -6205,7 +6253,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6214,16 +6262,16 @@
         <v>87</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6234,10 +6282,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6260,15 +6308,17 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>317</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -6317,7 +6367,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>87</v>
@@ -6326,19 +6376,19 @@
         <v>87</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>99</v>
+        <v>236</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>77</v>
@@ -6346,10 +6396,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6372,16 +6422,16 @@
         <v>77</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6431,7 +6481,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6440,16 +6490,16 @@
         <v>87</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>99</v>
+        <v>236</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>77</v>
@@ -6460,10 +6510,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6486,16 +6536,16 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6545,7 +6595,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6554,16 +6604,16 @@
         <v>87</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>99</v>
+        <v>236</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>77</v>
+        <v>330</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -6574,10 +6624,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6600,13 +6650,13 @@
         <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6657,7 +6707,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6666,16 +6716,16 @@
         <v>79</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
@@ -6686,10 +6736,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6712,13 +6762,13 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6769,7 +6819,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6787,7 +6837,7 @@
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>170</v>
+        <v>108</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -6798,14 +6848,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6824,16 +6874,16 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>173</v>
+        <v>136</v>
       </c>
       <c r="M47" t="s" s="2">
         <v>174</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6871,19 +6921,19 @@
         <v>77</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>77</v>
+        <v>141</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6892,16 +6942,16 @@
         <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>170</v>
+        <v>101</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
@@ -6912,14 +6962,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -6938,19 +6988,19 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -6999,7 +7049,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7008,16 +7058,16 @@
         <v>79</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
@@ -7028,10 +7078,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7054,15 +7104,17 @@
         <v>77</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>340</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7111,7 +7163,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7120,16 +7172,16 @@
         <v>87</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
@@ -7140,10 +7192,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7166,13 +7218,13 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7223,7 +7275,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>87</v>
@@ -7232,16 +7284,16 @@
         <v>87</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
@@ -7252,10 +7304,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7278,13 +7330,13 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7335,7 +7387,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7344,16 +7396,16 @@
         <v>79</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -7364,10 +7416,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7390,13 +7442,13 @@
         <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7447,7 +7499,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7465,7 +7517,7 @@
         <v>77</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>170</v>
+        <v>108</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>77</v>
@@ -7476,14 +7528,14 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7502,16 +7554,16 @@
         <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>173</v>
+        <v>136</v>
       </c>
       <c r="M53" t="s" s="2">
         <v>174</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7549,19 +7601,19 @@
         <v>77</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>77</v>
+        <v>141</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7570,16 +7622,16 @@
         <v>79</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>170</v>
+        <v>101</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
@@ -7590,14 +7642,14 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7616,19 +7668,19 @@
         <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -7677,7 +7729,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7686,16 +7738,16 @@
         <v>79</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
@@ -7706,10 +7758,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7732,15 +7784,17 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>354</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -7765,13 +7819,13 @@
         <v>77</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>77</v>
@@ -7789,7 +7843,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>87</v>
@@ -7798,30 +7852,30 @@
         <v>87</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7844,15 +7898,17 @@
         <v>77</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>359</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>77</v>
@@ -7901,7 +7957,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -7910,30 +7966,30 @@
         <v>87</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7956,16 +8012,16 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8015,7 +8071,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8024,16 +8080,16 @@
         <v>87</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
@@ -8044,10 +8100,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8070,16 +8126,16 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8129,7 +8185,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8138,16 +8194,16 @@
         <v>87</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>77</v>
+        <v>370</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>77</v>
@@ -8158,10 +8214,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8187,10 +8243,10 @@
         <v>80</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8241,7 +8297,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8253,13 +8309,13 @@
         <v>77</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>77</v>
@@ -8270,10 +8326,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8296,16 +8352,16 @@
         <v>88</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8355,7 +8411,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8364,16 +8420,16 @@
         <v>87</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>77</v>
+        <v>370</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
@@ -8384,10 +8440,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8410,16 +8466,16 @@
         <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8469,7 +8525,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8478,16 +8534,16 @@
         <v>87</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>77</v>
+        <v>370</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
@@ -8498,10 +8554,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8524,16 +8580,16 @@
         <v>77</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8583,7 +8639,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8592,16 +8648,16 @@
         <v>87</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
@@ -8612,10 +8668,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8638,15 +8694,17 @@
         <v>77</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>388</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>389</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -8695,7 +8753,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8704,22 +8762,22 @@
         <v>79</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>383</v>
+        <v>392</v>
       </c>
     </row>
   </sheetData>

--- a/main/ig/StructureDefinition-dmi-invoice.xlsx
+++ b/main/ig/StructureDefinition-dmi-invoice.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2309" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2295" uniqueCount="384">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:01:25+00:00</t>
+    <t>2026-03-05T10:22:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -266,7 +266,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>FT1</t>
@@ -316,172 +316,163 @@
     <t>Resource.meta</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
+    <t>Invoice.implicitRules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uri
+</t>
+  </si>
+  <si>
+    <t>A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+  </si>
+  <si>
+    <t>Resource.implicitRules</t>
+  </si>
+  <si>
+    <t>Invoice.language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Language of the resource content</t>
+  </si>
+  <si>
+    <t>The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>A human language.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+  </si>
+  <si>
+    <t>Resource.language</t>
+  </si>
+  <si>
+    <t>Invoice.text</t>
+  </si>
+  <si>
+    <t>narrative
+htmlxhtmldisplay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narrative
+</t>
+  </si>
+  <si>
+    <t>Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+  </si>
+  <si>
+    <t>DomainResource.text</t>
+  </si>
+  <si>
+    <t>Act.text?</t>
+  </si>
+  <si>
+    <t>Invoice.contained</t>
+  </si>
+  <si>
+    <t>inline resources
+anonymous resourcescontained resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+  </si>
+  <si>
+    <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Invoice.extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Invoice.extension:Facture</t>
+  </si>
+  <si>
+    <t>Facture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tdmi/StructureDefinition/dmi-facture}
+</t>
+  </si>
+  <si>
+    <t>DMI Facture</t>
+  </si>
+  <si>
+    <t>Extension créée dans ce volet pour représenter une facture.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Invoice.implicitRules</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uri
-</t>
-  </si>
-  <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
-  </si>
-  <si>
-    <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Invoice.language</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
-  </si>
-  <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>A human language.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
-  </si>
-  <si>
-    <t>Resource.language</t>
-  </si>
-  <si>
-    <t>Invoice.text</t>
-  </si>
-  <si>
-    <t>narrative
-htmlxhtmldisplay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative
-</t>
-  </si>
-  <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
-  </si>
-  <si>
-    <t>DomainResource.text</t>
-  </si>
-  <si>
-    <t>Act.text?</t>
-  </si>
-  <si>
-    <t>Invoice.contained</t>
-  </si>
-  <si>
-    <t>inline resources
-anonymous resourcescontained resources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
-  </si>
-  <si>
-    <t>DomainResource.contained</t>
-  </si>
-  <si>
-    <t>Invoice.extension</t>
+    <t>Invoice.modifierExtension</t>
   </si>
   <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Invoice.extension:Facture</t>
-  </si>
-  <si>
-    <t>Facture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tdmi/StructureDefinition/dmi-facture}
-</t>
-  </si>
-  <si>
-    <t>DMI Facture</t>
-  </si>
-  <si>
-    <t>Extension créée dans ce volet pour représenter une facture.</t>
-  </si>
-  <si>
-    <t>Invoice.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -489,6 +480,9 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -552,13 +546,22 @@
     <t>Element.id</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>Invoice.identifier:refFacture.extension</t>
   </si>
   <si>
     <t>Invoice.identifier.extension</t>
   </si>
   <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -715,15 +718,7 @@
     <t>Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
-    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
-Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
-  </si>
-  <si>
     <t>Identifier.period</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
   </si>
   <si>
     <t>CX.7 + CX.8</t>
@@ -752,10 +747,6 @@
   </si>
   <si>
     <t>Identifier.assigner</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
@@ -811,9 +802,6 @@
     <t>The current state of the Invoice.</t>
   </si>
   <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
     <t>Codes identifying the lifecycle stage of an Invoice.</t>
   </si>
   <si>
@@ -854,9 +842,6 @@
     <t>Type of Invoice depending on domain, realm an usage (e.g. internal/external, dental, preliminary).</t>
   </si>
   <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
-  </si>
-  <si>
     <t>FT1.7</t>
   </si>
   <si>
@@ -886,9 +871,6 @@
     <t>The individual or set of individuals receiving the goods and services billed in this invoice.</t>
   </si>
   <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
     <t>Links the event to the Patient context.</t>
   </si>
   <si>
@@ -1052,9 +1034,6 @@
     <t>Systems posting the ChargeItems might not always be able to determine, which accounts the Items need to be places into. It is up to the potprocessing Financial System to apply internal rules to decide based on the Encounter/EpisodeOfCare/Patient/Coverage context and the type of ChargeItem, which Account is appropriate.</t>
   </si>
   <si>
-    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
-  </si>
-  <si>
     <t>Invoice.lineItem</t>
   </si>
   <si>
@@ -1086,9 +1065,6 @@
     <t>Sequence in which the items appear on the invoice.</t>
   </si>
   <si>
-    <t>32 bit number; for values larger than this, use decimal</t>
-  </si>
-  <si>
     <t>Invoice.lineItem.chargeItem[x]</t>
   </si>
   <si>
@@ -1176,9 +1152,6 @@
     <t>The amount calculated for this component.</t>
   </si>
   <si>
-    <t>MO</t>
-  </si>
-  <si>
     <t>Invoice.totalPriceComponent</t>
   </si>
   <si>
@@ -1233,9 +1206,6 @@
   </si>
   <si>
     <t>Comments made about the invoice by the issuer, subject, or other participants.</t>
-  </si>
-  <si>
-    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
   </si>
   <si>
     <t>NTE</t>
@@ -2032,16 +2002,16 @@
         <v>87</v>
       </c>
       <c r="AI4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ4" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AM4" t="s" s="2">
         <v>77</v>
@@ -2052,10 +2022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2078,16 +2048,16 @@
         <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L5" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="M5" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>106</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2137,7 +2107,7 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -2146,16 +2116,16 @@
         <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ5" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ5" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AM5" t="s" s="2">
         <v>77</v>
@@ -2166,10 +2136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2192,16 +2162,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L6" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M6" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="N6" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="L6" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2227,32 +2197,32 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="Y6" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="Y6" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Z6" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>117</v>
-      </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
@@ -2260,16 +2230,16 @@
         <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ6" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ6" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AM6" t="s" s="2">
         <v>77</v>
@@ -2280,14 +2250,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2306,16 +2276,16 @@
         <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="M7" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="N7" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="L7" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2365,7 +2335,7 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -2374,16 +2344,16 @@
         <v>87</v>
       </c>
       <c r="AI7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ7" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>77</v>
@@ -2394,14 +2364,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2420,16 +2390,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="M8" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="N8" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="L8" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2479,7 +2449,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2497,7 +2467,7 @@
         <v>77</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>77</v>
@@ -2508,14 +2478,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2534,17 +2504,15 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>77</v>
@@ -2581,19 +2549,17 @@
         <v>77</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2602,16 +2568,16 @@
         <v>79</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>77</v>
@@ -2622,13 +2588,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>77</v>
@@ -2650,13 +2616,13 @@
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2707,7 +2673,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2716,10 +2682,10 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>99</v>
+        <v>144</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
@@ -2736,14 +2702,14 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2762,19 +2728,19 @@
         <v>77</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="L11" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M11" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="O11" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>77</v>
@@ -2811,19 +2777,19 @@
         <v>77</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>140</v>
+        <v>77</v>
       </c>
       <c r="AD11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2832,16 +2798,16 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>77</v>
@@ -2852,10 +2818,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2863,7 +2829,7 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>79</v>
@@ -2878,17 +2844,17 @@
         <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>158</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -2925,17 +2891,17 @@
         <v>77</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="AC12" s="2"/>
       <c r="AD12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2944,19 +2910,19 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ12" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK12" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AM12" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>77</v>
@@ -2964,13 +2930,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>77</v>
@@ -2992,17 +2958,17 @@
         <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="L13" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>158</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>77</v>
@@ -3051,7 +3017,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3060,19 +3026,19 @@
         <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ13" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK13" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>77</v>
@@ -3080,10 +3046,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3106,13 +3072,13 @@
         <v>77</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="L14" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3163,7 +3129,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3181,7 +3147,7 @@
         <v>77</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>108</v>
+        <v>170</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>77</v>
@@ -3192,14 +3158,14 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3218,16 +3184,16 @@
         <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="M15" t="s" s="2">
         <v>174</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3265,19 +3231,19 @@
         <v>77</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3286,16 +3252,16 @@
         <v>79</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>101</v>
+        <v>170</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>77</v>
@@ -3306,10 +3272,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3332,19 +3298,19 @@
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3369,13 +3335,13 @@
         <v>77</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>77</v>
@@ -3393,7 +3359,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3402,16 +3368,16 @@
         <v>87</v>
       </c>
       <c r="AI16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ16" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK16" t="s" s="2">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
@@ -3422,10 +3388,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3448,19 +3414,19 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>77</v>
@@ -3470,7 +3436,7 @@
         <v>77</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>77</v>
@@ -3485,13 +3451,13 @@
         <v>77</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>77</v>
@@ -3509,7 +3475,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3518,16 +3484,16 @@
         <v>87</v>
       </c>
       <c r="AI17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ17" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
@@ -3538,10 +3504,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3564,19 +3530,19 @@
         <v>88</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -3589,7 +3555,7 @@
         <v>77</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>77</v>
@@ -3625,7 +3591,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3634,16 +3600,16 @@
         <v>87</v>
       </c>
       <c r="AI18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ18" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -3654,10 +3620,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3680,16 +3646,16 @@
         <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3703,7 +3669,7 @@
         <v>77</v>
       </c>
       <c r="T19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="U19" t="s" s="2">
         <v>77</v>
@@ -3739,7 +3705,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3748,16 +3714,16 @@
         <v>87</v>
       </c>
       <c r="AI19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ19" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -3768,10 +3734,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3794,17 +3760,15 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N20" t="s" s="2">
         <v>224</v>
       </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>77</v>
@@ -3862,16 +3826,16 @@
         <v>87</v>
       </c>
       <c r="AI20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ20" t="s" s="2">
+      <c r="AK20" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="AK20" t="s" s="2">
+      <c r="AL20" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
@@ -3882,10 +3846,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3908,16 +3872,16 @@
         <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3967,25 +3931,25 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK21" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="AG21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH21" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI21" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ21" t="s" s="2">
+      <c r="AL21" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="AK21" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
@@ -3996,13 +3960,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>77</v>
@@ -4024,17 +3988,17 @@
         <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="L22" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>158</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -4083,7 +4047,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4092,19 +4056,19 @@
         <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ22" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK22" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="AL22" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>77</v>
@@ -4112,10 +4076,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4138,13 +4102,13 @@
         <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4195,7 +4159,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4213,7 +4177,7 @@
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>108</v>
+        <v>170</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -4224,14 +4188,14 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4250,16 +4214,16 @@
         <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="M24" t="s" s="2">
         <v>174</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4297,19 +4261,19 @@
         <v>77</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4318,16 +4282,16 @@
         <v>79</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>101</v>
+        <v>170</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -4338,10 +4302,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4364,19 +4328,19 @@
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4401,13 +4365,13 @@
         <v>77</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>77</v>
@@ -4425,7 +4389,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4434,16 +4398,16 @@
         <v>87</v>
       </c>
       <c r="AI25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ25" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK25" t="s" s="2">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4454,10 +4418,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4480,19 +4444,19 @@
         <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4502,7 +4466,7 @@
         <v>77</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>77</v>
@@ -4517,13 +4481,13 @@
         <v>77</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>77</v>
@@ -4541,7 +4505,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4550,16 +4514,16 @@
         <v>87</v>
       </c>
       <c r="AI26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ26" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK26" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4570,10 +4534,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4596,19 +4560,19 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4621,7 +4585,7 @@
         <v>77</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>77</v>
@@ -4657,7 +4621,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4666,16 +4630,16 @@
         <v>87</v>
       </c>
       <c r="AI27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ27" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK27" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -4686,10 +4650,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4712,16 +4676,16 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4735,7 +4699,7 @@
         <v>77</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>77</v>
@@ -4771,7 +4735,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4780,16 +4744,16 @@
         <v>87</v>
       </c>
       <c r="AI28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ28" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK28" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -4800,10 +4764,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4826,17 +4790,15 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N29" t="s" s="2">
         <v>224</v>
       </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -4894,16 +4856,16 @@
         <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ29" t="s" s="2">
+      <c r="AK29" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="AK29" t="s" s="2">
+      <c r="AL29" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
@@ -4914,10 +4876,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4940,16 +4902,16 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4999,25 +4961,25 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK30" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="AG30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ30" t="s" s="2">
+      <c r="AL30" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="AK30" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
@@ -5028,10 +4990,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5054,17 +5016,15 @@
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -5089,52 +5049,52 @@
         <v>77</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Y31" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AL31" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="Z31" t="s" s="2">
+      <c r="AM31" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="AA31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="AG31" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH31" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI31" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK31" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -5142,10 +5102,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5168,16 +5128,16 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5227,7 +5187,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5236,16 +5196,16 @@
         <v>87</v>
       </c>
       <c r="AI32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ32" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -5256,14 +5216,14 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5282,17 +5242,15 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5341,7 +5299,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5350,34 +5308,34 @@
         <v>87</v>
       </c>
       <c r="AI33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ33" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK33" t="s" s="2">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5396,19 +5354,17 @@
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>277</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5457,7 +5413,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5466,30 +5422,30 @@
         <v>87</v>
       </c>
       <c r="AI34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ34" t="s" s="2">
-        <v>236</v>
-      </c>
       <c r="AK34" t="s" s="2">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>282</v>
+        <v>277</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5512,17 +5468,15 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>277</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5571,39 +5525,39 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AG35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI35" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ35" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="AK35" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>288</v>
-      </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>289</v>
+        <v>284</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5626,16 +5580,16 @@
         <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5685,28 +5639,28 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AL36" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AG36" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH36" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI36" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ36" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK36" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>295</v>
-      </c>
       <c r="AM36" t="s" s="2">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>77</v>
@@ -5714,10 +5668,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5740,13 +5694,13 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5797,7 +5751,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5806,16 +5760,16 @@
         <v>79</v>
       </c>
       <c r="AI37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ37" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK37" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -5826,10 +5780,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5852,13 +5806,13 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="L38" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5909,7 +5863,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5927,7 +5881,7 @@
         <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>108</v>
+        <v>170</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
@@ -5938,14 +5892,14 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -5964,16 +5918,16 @@
         <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="M39" t="s" s="2">
         <v>174</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6011,19 +5965,19 @@
         <v>77</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>140</v>
+        <v>77</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6032,16 +5986,16 @@
         <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>101</v>
+        <v>170</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
@@ -6052,14 +6006,14 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6078,19 +6032,19 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>77</v>
@@ -6139,7 +6093,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6148,16 +6102,16 @@
         <v>79</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -6168,10 +6122,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6194,17 +6148,15 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>77</v>
@@ -6253,7 +6205,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6262,16 +6214,16 @@
         <v>87</v>
       </c>
       <c r="AI41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ41" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK41" t="s" s="2">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6282,10 +6234,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6308,17 +6260,15 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>277</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -6367,28 +6317,28 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AG42" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH42" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI42" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ42" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="AK42" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>77</v>
@@ -6396,10 +6346,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6422,16 +6372,16 @@
         <v>77</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6481,7 +6431,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6490,16 +6440,16 @@
         <v>87</v>
       </c>
       <c r="AI43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ43" t="s" s="2">
-        <v>236</v>
-      </c>
       <c r="AK43" t="s" s="2">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>77</v>
@@ -6510,10 +6460,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6536,16 +6486,16 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6595,7 +6545,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6604,16 +6554,16 @@
         <v>87</v>
       </c>
       <c r="AI44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ44" t="s" s="2">
-        <v>236</v>
-      </c>
       <c r="AK44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>330</v>
+        <v>77</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -6624,10 +6574,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6650,13 +6600,13 @@
         <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6707,7 +6657,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6716,16 +6666,16 @@
         <v>79</v>
       </c>
       <c r="AI45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ45" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK45" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
@@ -6736,10 +6686,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6762,13 +6712,13 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6819,7 +6769,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6837,7 +6787,7 @@
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>108</v>
+        <v>170</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -6848,14 +6798,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6874,16 +6824,16 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="M47" t="s" s="2">
         <v>174</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6921,19 +6871,19 @@
         <v>77</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>140</v>
+        <v>77</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6942,16 +6892,16 @@
         <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>101</v>
+        <v>170</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
@@ -6962,14 +6912,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -6988,19 +6938,19 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -7049,7 +6999,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7058,16 +7008,16 @@
         <v>79</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
@@ -7078,10 +7028,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7104,17 +7054,15 @@
         <v>77</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>341</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7163,7 +7111,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7172,16 +7120,16 @@
         <v>87</v>
       </c>
       <c r="AI49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ49" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
@@ -7192,10 +7140,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7218,13 +7166,13 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7275,7 +7223,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>87</v>
@@ -7284,16 +7232,16 @@
         <v>87</v>
       </c>
       <c r="AI50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ50" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK50" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
@@ -7304,10 +7252,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7330,13 +7278,13 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7387,7 +7335,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7396,16 +7344,16 @@
         <v>79</v>
       </c>
       <c r="AI51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ51" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK51" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -7416,10 +7364,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7442,13 +7390,13 @@
         <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7499,7 +7447,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7517,7 +7465,7 @@
         <v>77</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>108</v>
+        <v>170</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>77</v>
@@ -7528,14 +7476,14 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7554,16 +7502,16 @@
         <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="M53" t="s" s="2">
         <v>174</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7601,19 +7549,19 @@
         <v>77</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>140</v>
+        <v>77</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7622,16 +7570,16 @@
         <v>79</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>101</v>
+        <v>170</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
@@ -7642,14 +7590,14 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7668,19 +7616,19 @@
         <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -7729,7 +7677,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7738,16 +7686,16 @@
         <v>79</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
@@ -7758,10 +7706,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7784,17 +7732,15 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -7819,13 +7765,13 @@
         <v>77</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>77</v>
@@ -7843,7 +7789,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>87</v>
@@ -7852,30 +7798,30 @@
         <v>87</v>
       </c>
       <c r="AI55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ55" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK55" t="s" s="2">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7898,17 +7844,15 @@
         <v>77</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>77</v>
@@ -7957,7 +7901,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -7966,30 +7910,30 @@
         <v>87</v>
       </c>
       <c r="AI56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ56" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK56" t="s" s="2">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8012,16 +7956,16 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8071,7 +8015,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8080,16 +8024,16 @@
         <v>87</v>
       </c>
       <c r="AI57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ57" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK57" t="s" s="2">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
@@ -8100,10 +8044,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8126,16 +8070,16 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8185,7 +8129,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8194,16 +8138,16 @@
         <v>87</v>
       </c>
       <c r="AI58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ58" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK58" t="s" s="2">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>370</v>
+        <v>77</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>77</v>
@@ -8214,10 +8158,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8243,10 +8187,10 @@
         <v>80</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8297,7 +8241,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8309,13 +8253,13 @@
         <v>77</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>77</v>
@@ -8326,10 +8270,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8352,16 +8296,16 @@
         <v>88</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="L60" t="s" s="2">
-        <v>375</v>
-      </c>
       <c r="M60" t="s" s="2">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8411,7 +8355,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8420,16 +8364,16 @@
         <v>87</v>
       </c>
       <c r="AI60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ60" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK60" t="s" s="2">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>370</v>
+        <v>77</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
@@ -8440,10 +8384,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8466,16 +8410,16 @@
         <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8525,7 +8469,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8534,16 +8478,16 @@
         <v>87</v>
       </c>
       <c r="AI61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ61" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK61" t="s" s="2">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>370</v>
+        <v>77</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
@@ -8554,10 +8498,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8580,16 +8524,16 @@
         <v>77</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8639,7 +8583,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8648,16 +8592,16 @@
         <v>87</v>
       </c>
       <c r="AI62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ62" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
@@ -8668,10 +8612,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8694,17 +8638,15 @@
         <v>77</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>389</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -8753,7 +8695,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8762,22 +8704,22 @@
         <v>79</v>
       </c>
       <c r="AI63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ63" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK63" t="s" s="2">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>392</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>

--- a/main/ig/StructureDefinition-dmi-invoice.xlsx
+++ b/main/ig/StructureDefinition-dmi-invoice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:22:34+00:00</t>
+    <t>2026-03-05T10:23:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-invoice.xlsx
+++ b/main/ig/StructureDefinition-dmi-invoice.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2295" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2309" uniqueCount="393">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:23:55+00:00</t>
+    <t>2026-03-05T10:25:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -266,7 +266,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
   </si>
   <si>
     <t>FT1</t>
@@ -316,10 +316,17 @@
     <t>Resource.meta</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>Invoice.implicitRules</t>
   </si>
   <si>
@@ -339,6 +346,9 @@
     <t>Resource.implicitRules</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>Invoice.language</t>
   </si>
   <si>
@@ -416,26 +426,33 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Invoice.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
   </si>
   <si>
     <t xml:space="preserve">Extension
 </t>
   </si>
   <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
 </t>
   </si>
   <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
     <t>open</t>
   </si>
   <si>
@@ -462,15 +479,7 @@
     <t>Extension créée dans ce volet pour représenter une facture.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>Invoice.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
   </si>
   <si>
     <t>Extensions that cannot be ignored</t>
@@ -480,9 +489,6 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -546,22 +552,13 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Invoice.identifier:refFacture.extension</t>
   </si>
   <si>
     <t>Invoice.identifier.extension</t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -718,7 +715,15 @@
     <t>Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
+    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
+Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
+  </si>
+  <si>
     <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
   </si>
   <si>
     <t>CX.7 + CX.8</t>
@@ -747,6 +752,10 @@
   </si>
   <si>
     <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
@@ -802,6 +811,9 @@
     <t>The current state of the Invoice.</t>
   </si>
   <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
     <t>Codes identifying the lifecycle stage of an Invoice.</t>
   </si>
   <si>
@@ -842,6 +854,9 @@
     <t>Type of Invoice depending on domain, realm an usage (e.g. internal/external, dental, preliminary).</t>
   </si>
   <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+  </si>
+  <si>
     <t>FT1.7</t>
   </si>
   <si>
@@ -871,6 +886,9 @@
     <t>The individual or set of individuals receiving the goods and services billed in this invoice.</t>
   </si>
   <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
     <t>Links the event to the Patient context.</t>
   </si>
   <si>
@@ -1034,6 +1052,9 @@
     <t>Systems posting the ChargeItems might not always be able to determine, which accounts the Items need to be places into. It is up to the potprocessing Financial System to apply internal rules to decide based on the Encounter/EpisodeOfCare/Patient/Coverage context and the type of ChargeItem, which Account is appropriate.</t>
   </si>
   <si>
+    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
+  </si>
+  <si>
     <t>Invoice.lineItem</t>
   </si>
   <si>
@@ -1065,6 +1086,9 @@
     <t>Sequence in which the items appear on the invoice.</t>
   </si>
   <si>
+    <t>32 bit number; for values larger than this, use decimal</t>
+  </si>
+  <si>
     <t>Invoice.lineItem.chargeItem[x]</t>
   </si>
   <si>
@@ -1152,6 +1176,9 @@
     <t>The amount calculated for this component.</t>
   </si>
   <si>
+    <t>MO</t>
+  </si>
+  <si>
     <t>Invoice.totalPriceComponent</t>
   </si>
   <si>
@@ -1206,6 +1233,9 @@
   </si>
   <si>
     <t>Comments made about the invoice by the issuer, subject, or other participants.</t>
+  </si>
+  <si>
+    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
   </si>
   <si>
     <t>NTE</t>
@@ -2002,16 +2032,16 @@
         <v>87</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AM4" t="s" s="2">
         <v>77</v>
@@ -2022,10 +2052,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2048,16 +2078,16 @@
         <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2107,7 +2137,7 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -2116,16 +2146,16 @@
         <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AM5" t="s" s="2">
         <v>77</v>
@@ -2136,10 +2166,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2162,16 +2192,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2197,13 +2227,13 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>77</v>
@@ -2221,7 +2251,7 @@
         <v>77</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
@@ -2230,16 +2260,16 @@
         <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AM6" t="s" s="2">
         <v>77</v>
@@ -2250,14 +2280,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2276,16 +2306,16 @@
         <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2335,7 +2365,7 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -2344,16 +2374,16 @@
         <v>87</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>77</v>
@@ -2364,14 +2394,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2390,16 +2420,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2449,7 +2479,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2467,7 +2497,7 @@
         <v>77</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>77</v>
@@ -2478,14 +2508,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2504,15 +2534,17 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="N9" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>77</v>
@@ -2549,17 +2581,19 @@
         <v>77</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AC9" s="2"/>
+        <v>139</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="AD9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2568,16 +2602,16 @@
         <v>79</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>77</v>
@@ -2588,13 +2622,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>77</v>
@@ -2616,13 +2650,13 @@
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2673,7 +2707,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2682,10 +2716,10 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>144</v>
+        <v>99</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
@@ -2702,14 +2736,14 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2728,19 +2762,19 @@
         <v>77</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>77</v>
@@ -2777,19 +2811,19 @@
         <v>77</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="AD11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>77</v>
+        <v>141</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2798,16 +2832,16 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>77</v>
@@ -2818,10 +2852,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2829,7 +2863,7 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>79</v>
@@ -2844,17 +2878,17 @@
         <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -2891,17 +2925,17 @@
         <v>77</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AC12" s="2"/>
       <c r="AD12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2910,19 +2944,19 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>77</v>
@@ -2930,13 +2964,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>77</v>
@@ -2958,17 +2992,17 @@
         <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>77</v>
@@ -3017,7 +3051,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3026,19 +3060,19 @@
         <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>77</v>
@@ -3046,10 +3080,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3072,13 +3106,13 @@
         <v>77</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3129,7 +3163,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3147,7 +3181,7 @@
         <v>77</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>170</v>
+        <v>108</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>77</v>
@@ -3158,14 +3192,14 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3184,16 +3218,16 @@
         <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>173</v>
+        <v>136</v>
       </c>
       <c r="M15" t="s" s="2">
         <v>174</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3231,19 +3265,19 @@
         <v>77</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="AC15" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3252,16 +3286,16 @@
         <v>79</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>170</v>
+        <v>101</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>77</v>
@@ -3272,10 +3306,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3298,19 +3332,19 @@
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3335,49 +3369,49 @@
         <v>77</v>
       </c>
       <c r="X16" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Y16" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="Z16" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="Z16" t="s" s="2">
+      <c r="AA16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="AA16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF16" t="s" s="2">
+      <c r="AG16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK16" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AL16" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK16" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
@@ -3388,10 +3422,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3414,19 +3448,19 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>77</v>
@@ -3436,64 +3470,64 @@
         <v>77</v>
       </c>
       <c r="S17" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X17" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="T17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X17" t="s" s="2">
+      <c r="Y17" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="Y17" t="s" s="2">
+      <c r="Z17" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="Z17" t="s" s="2">
+      <c r="AA17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AA17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF17" t="s" s="2">
+      <c r="AG17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK17" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="AG17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK17" t="s" s="2">
-        <v>200</v>
-      </c>
       <c r="AL17" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
@@ -3504,10 +3538,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>202</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3530,19 +3564,19 @@
         <v>88</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -3555,61 +3589,61 @@
         <v>77</v>
       </c>
       <c r="T18" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="U18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF18" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="U18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF18" t="s" s="2">
+      <c r="AG18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK18" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="AG18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK18" t="s" s="2">
+      <c r="AL18" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -3620,10 +3654,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3646,16 +3680,16 @@
         <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3669,61 +3703,61 @@
         <v>77</v>
       </c>
       <c r="T19" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF19" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="U19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF19" t="s" s="2">
+      <c r="AG19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK19" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="AG19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH19" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ19" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK19" t="s" s="2">
+      <c r="AL19" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -3734,10 +3768,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3760,15 +3794,17 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>77</v>
@@ -3826,16 +3862,16 @@
         <v>87</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>99</v>
+        <v>226</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
@@ -3846,10 +3882,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3872,16 +3908,16 @@
         <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3931,7 +3967,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3940,16 +3976,16 @@
         <v>87</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>99</v>
+        <v>236</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
@@ -3960,13 +3996,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>77</v>
@@ -3988,17 +4024,17 @@
         <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -4047,7 +4083,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4056,19 +4092,19 @@
         <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>77</v>
@@ -4076,10 +4112,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4102,13 +4138,13 @@
         <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4159,7 +4195,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4177,7 +4213,7 @@
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>170</v>
+        <v>108</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -4188,14 +4224,14 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4214,16 +4250,16 @@
         <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>173</v>
+        <v>136</v>
       </c>
       <c r="M24" t="s" s="2">
         <v>174</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4261,19 +4297,19 @@
         <v>77</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="AC24" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AF24" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4282,16 +4318,16 @@
         <v>79</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>170</v>
+        <v>101</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -4302,10 +4338,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4328,19 +4364,19 @@
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4365,49 +4401,49 @@
         <v>77</v>
       </c>
       <c r="X25" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Y25" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="Y25" t="s" s="2">
+      <c r="Z25" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="Z25" t="s" s="2">
+      <c r="AA25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="AA25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF25" t="s" s="2">
+      <c r="AG25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AL25" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="AG25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ25" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK25" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4418,10 +4454,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4444,19 +4480,19 @@
         <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4466,7 +4502,7 @@
         <v>77</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>77</v>
@@ -4481,49 +4517,49 @@
         <v>77</v>
       </c>
       <c r="X26" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="Y26" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="Y26" t="s" s="2">
+      <c r="Z26" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="Z26" t="s" s="2">
+      <c r="AA26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AA26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF26" t="s" s="2">
+      <c r="AG26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK26" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="AG26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ26" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK26" t="s" s="2">
-        <v>200</v>
-      </c>
       <c r="AL26" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4534,10 +4570,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4560,19 +4596,19 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4585,61 +4621,61 @@
         <v>77</v>
       </c>
       <c r="T27" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="U27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF27" t="s" s="2">
+      <c r="AG27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK27" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="AG27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ27" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK27" t="s" s="2">
+      <c r="AL27" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -4650,10 +4686,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4676,16 +4712,16 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4699,61 +4735,61 @@
         <v>77</v>
       </c>
       <c r="T28" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="U28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF28" t="s" s="2">
+      <c r="AG28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK28" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="AG28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK28" t="s" s="2">
+      <c r="AL28" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -4764,10 +4800,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4790,15 +4826,17 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -4856,16 +4894,16 @@
         <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>99</v>
+        <v>226</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
@@ -4876,10 +4914,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4902,16 +4940,16 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4961,7 +4999,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4970,16 +5008,16 @@
         <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>99</v>
+        <v>236</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
@@ -4990,10 +5028,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5016,15 +5054,17 @@
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -5049,13 +5089,13 @@
         <v>77</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>77</v>
@@ -5073,7 +5113,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>87</v>
@@ -5082,19 +5122,19 @@
         <v>87</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -5102,10 +5142,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5128,16 +5168,16 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5187,7 +5227,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5196,16 +5236,16 @@
         <v>87</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -5216,14 +5256,14 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5242,15 +5282,17 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5299,7 +5341,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5308,34 +5350,34 @@
         <v>87</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5354,17 +5396,19 @@
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="O34" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5413,7 +5457,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5422,30 +5466,30 @@
         <v>87</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>99</v>
+        <v>236</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5468,15 +5512,17 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5525,7 +5571,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5534,30 +5580,30 @@
         <v>87</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>99</v>
+        <v>236</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5580,16 +5626,16 @@
         <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5639,7 +5685,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5648,19 +5694,19 @@
         <v>87</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>77</v>
@@ -5668,10 +5714,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5694,13 +5740,13 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5751,7 +5797,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5760,16 +5806,16 @@
         <v>79</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -5780,10 +5826,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5806,13 +5852,13 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5863,7 +5909,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5881,7 +5927,7 @@
         <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>170</v>
+        <v>108</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
@@ -5892,14 +5938,14 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -5918,16 +5964,16 @@
         <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>173</v>
+        <v>136</v>
       </c>
       <c r="M39" t="s" s="2">
         <v>174</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5965,19 +6011,19 @@
         <v>77</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>77</v>
+        <v>141</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5986,16 +6032,16 @@
         <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>170</v>
+        <v>101</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
@@ -6006,14 +6052,14 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6032,19 +6078,19 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>77</v>
@@ -6093,7 +6139,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6102,16 +6148,16 @@
         <v>79</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -6122,10 +6168,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6148,15 +6194,17 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>77</v>
@@ -6205,7 +6253,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6214,16 +6262,16 @@
         <v>87</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6234,10 +6282,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6260,15 +6308,17 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>317</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -6317,7 +6367,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>87</v>
@@ -6326,19 +6376,19 @@
         <v>87</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>99</v>
+        <v>236</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>77</v>
@@ -6346,10 +6396,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6372,16 +6422,16 @@
         <v>77</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6431,7 +6481,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6440,16 +6490,16 @@
         <v>87</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>99</v>
+        <v>236</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>77</v>
@@ -6460,10 +6510,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6486,16 +6536,16 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6545,7 +6595,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6554,16 +6604,16 @@
         <v>87</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>99</v>
+        <v>236</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>77</v>
+        <v>330</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -6574,10 +6624,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6600,13 +6650,13 @@
         <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6657,7 +6707,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6666,16 +6716,16 @@
         <v>79</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
@@ -6686,10 +6736,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6712,13 +6762,13 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6769,7 +6819,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6787,7 +6837,7 @@
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>170</v>
+        <v>108</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -6798,14 +6848,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6824,16 +6874,16 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>173</v>
+        <v>136</v>
       </c>
       <c r="M47" t="s" s="2">
         <v>174</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6871,19 +6921,19 @@
         <v>77</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>77</v>
+        <v>141</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6892,16 +6942,16 @@
         <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>170</v>
+        <v>101</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
@@ -6912,14 +6962,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -6938,19 +6988,19 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -6999,7 +7049,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7008,16 +7058,16 @@
         <v>79</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
@@ -7028,10 +7078,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7054,15 +7104,17 @@
         <v>77</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>340</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7111,7 +7163,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7120,16 +7172,16 @@
         <v>87</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
@@ -7140,10 +7192,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7166,13 +7218,13 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7223,7 +7275,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>87</v>
@@ -7232,16 +7284,16 @@
         <v>87</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
@@ -7252,10 +7304,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7278,13 +7330,13 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7335,7 +7387,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7344,16 +7396,16 @@
         <v>79</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -7364,10 +7416,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7390,13 +7442,13 @@
         <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7447,7 +7499,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7465,7 +7517,7 @@
         <v>77</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>170</v>
+        <v>108</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>77</v>
@@ -7476,14 +7528,14 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7502,16 +7554,16 @@
         <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>173</v>
+        <v>136</v>
       </c>
       <c r="M53" t="s" s="2">
         <v>174</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7549,19 +7601,19 @@
         <v>77</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>77</v>
+        <v>141</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7570,16 +7622,16 @@
         <v>79</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>170</v>
+        <v>101</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
@@ -7590,14 +7642,14 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7616,19 +7668,19 @@
         <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -7677,7 +7729,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7686,16 +7738,16 @@
         <v>79</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
@@ -7706,10 +7758,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7732,15 +7784,17 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>354</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -7765,13 +7819,13 @@
         <v>77</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>77</v>
@@ -7789,7 +7843,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>87</v>
@@ -7798,30 +7852,30 @@
         <v>87</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7844,15 +7898,17 @@
         <v>77</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>359</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>77</v>
@@ -7901,7 +7957,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -7910,30 +7966,30 @@
         <v>87</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7956,16 +8012,16 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8015,7 +8071,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8024,16 +8080,16 @@
         <v>87</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
@@ -8044,10 +8100,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8070,16 +8126,16 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8129,7 +8185,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8138,16 +8194,16 @@
         <v>87</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>77</v>
+        <v>370</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>77</v>
@@ -8158,10 +8214,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8187,10 +8243,10 @@
         <v>80</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8241,7 +8297,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8253,13 +8309,13 @@
         <v>77</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>77</v>
@@ -8270,10 +8326,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8296,16 +8352,16 @@
         <v>88</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8355,7 +8411,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8364,16 +8420,16 @@
         <v>87</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>77</v>
+        <v>370</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
@@ -8384,10 +8440,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8410,16 +8466,16 @@
         <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8469,7 +8525,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8478,16 +8534,16 @@
         <v>87</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>77</v>
+        <v>370</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
@@ -8498,10 +8554,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8524,16 +8580,16 @@
         <v>77</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8583,7 +8639,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8592,16 +8648,16 @@
         <v>87</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
@@ -8612,10 +8668,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8638,15 +8694,17 @@
         <v>77</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>388</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>389</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -8695,7 +8753,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8704,22 +8762,22 @@
         <v>79</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>383</v>
+        <v>392</v>
       </c>
     </row>
   </sheetData>
